--- a/ML - TURISMO/graficos/tabla_catboost_2.xlsx
+++ b/ML - TURISMO/graficos/tabla_catboost_2.xlsx
@@ -478,7 +478,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>5.353.107</t>
+          <t>5.522.149</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -488,7 +488,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>285.842</t>
+          <t>293.698</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -498,7 +498,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>110.905</t>
+          <t>114.016</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -508,7 +508,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>18.907</t>
+          <t>19.350</t>
         </is>
       </c>
     </row>
@@ -520,7 +520,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>3.396.226</t>
+          <t>3.432.050</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -530,27 +530,27 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>278.698</t>
+          <t>273.768</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Lugo</t>
+          <t>Castellón/Castelló</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>78.576</t>
+          <t>80.040</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Ciudad Real</t>
+          <t>Palencia</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>18.746</t>
+          <t>18.997</t>
         </is>
       </c>
     </row>
@@ -562,7 +562,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2.012.973</t>
+          <t>2.131.779</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -572,39 +572,39 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>262.439</t>
+          <t>266.157</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Castellón/Castelló</t>
+          <t>Lugo</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>78.274</t>
+          <t>79.801</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Palencia</t>
+          <t>Ciudad Real</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>18.629</t>
+          <t>18.832</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Las Palmas</t>
+          <t>Málaga</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>1.323.628</t>
+          <t>1.353.081</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -614,7 +614,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>215.816</t>
+          <t>228.796</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -624,29 +624,29 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>71.451</t>
+          <t>74.011</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Ourense</t>
+          <t>Teruel</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>15.827</t>
+          <t>16.166</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Málaga</t>
+          <t>Las Palmas</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>1.305.844</t>
+          <t>1.340.502</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -656,7 +656,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>168.153</t>
+          <t>169.359</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -666,7 +666,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>70.210</t>
+          <t>67.991</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -676,7 +676,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>15.546</t>
+          <t>16.021</t>
         </is>
       </c>
     </row>
@@ -688,7 +688,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>1.157.713</t>
+          <t>1.196.858</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -698,7 +698,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>147.319</t>
+          <t>157.449</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -708,17 +708,17 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>65.344</t>
+          <t>65.206</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Teruel</t>
+          <t>Ourense</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>15.521</t>
+          <t>16.019</t>
         </is>
       </c>
     </row>
@@ -730,7 +730,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>851.674</t>
+          <t>869.473</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -740,7 +740,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>144.012</t>
+          <t>156.408</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -750,7 +750,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>60.981</t>
+          <t>62.971</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>13.722</t>
+          <t>14.609</t>
         </is>
       </c>
     </row>
@@ -772,37 +772,37 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>830.911</t>
+          <t>864.084</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Murcia</t>
+          <t>Zaragoza</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>136.076</t>
+          <t>140.424</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Toledo</t>
+          <t>Badajoz</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>60.315</t>
+          <t>62.274</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Guadalajara</t>
+          <t>Cuenca</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>10.026</t>
+          <t>9.942</t>
         </is>
       </c>
     </row>
@@ -814,37 +814,37 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>689.607</t>
+          <t>670.809</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Zaragoza</t>
+          <t>Murcia</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>132.212</t>
+          <t>140.370</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>La Rioja</t>
+          <t>Toledo</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>58.888</t>
+          <t>61.460</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Cuenca</t>
+          <t>Guadalajara</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>9.774</t>
+          <t>9.645</t>
         </is>
       </c>
     </row>
@@ -856,27 +856,27 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>549.356</t>
+          <t>565.563</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Salamanca</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>131.902</t>
+          <t>133.759</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Badajoz</t>
+          <t>Valladolid</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>58.608</t>
+          <t>54.945</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -886,7 +886,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>9.080</t>
+          <t>9.420</t>
         </is>
       </c>
     </row>
@@ -898,27 +898,27 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>509.115</t>
+          <t>521.022</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Cantabria</t>
+          <t>Salamanca</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>131.350</t>
+          <t>133.612</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Valladolid</t>
+          <t>La Rioja</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>53.941</t>
+          <t>54.821</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -928,7 +928,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>7.773</t>
+          <t>8.693</t>
         </is>
       </c>
     </row>
@@ -940,17 +940,17 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>322.823</t>
+          <t>348.310</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>Cantabria</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>128.002</t>
+          <t>131.352</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -960,7 +960,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>40.777</t>
+          <t>39.225</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -970,7 +970,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>7.683</t>
+          <t>8.524</t>
         </is>
       </c>
     </row>
@@ -982,7 +982,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>294.004</t>
+          <t>300.346</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>120.419</t>
+          <t>116.762</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1002,7 +1002,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>31.279</t>
+          <t>29.954</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -1012,7 +1012,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>6.619</t>
+          <t>6.342</t>
         </is>
       </c>
     </row>

--- a/ML - TURISMO/graficos/tabla_catboost_2.xlsx
+++ b/ML - TURISMO/graficos/tabla_catboost_2.xlsx
@@ -478,17 +478,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>5.522.149</t>
+          <t>6.990.024</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Bizkaia</t>
+          <t>Granada</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>293.698</t>
+          <t>236.299</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -498,17 +498,17 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>114.016</t>
+          <t>104.495</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Jaén</t>
+          <t>Ciudad Real</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>19.350</t>
+          <t>16.359</t>
         </is>
       </c>
     </row>
@@ -520,7 +520,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>3.432.050</t>
+          <t>3.667.842</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -530,7 +530,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>273.768</t>
+          <t>220.094</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -540,17 +540,17 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>80.040</t>
+          <t>90.450</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Palencia</t>
+          <t>Jaén</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>18.997</t>
+          <t>15.389</t>
         </is>
       </c>
     </row>
@@ -562,91 +562,91 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2.131.779</t>
+          <t>1.603.836</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>A Coruña</t>
+          <t>Pontevedra</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>266.157</t>
+          <t>219.565</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Lugo</t>
+          <t>Huesca</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>79.801</t>
+          <t>83.515</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Ciudad Real</t>
+          <t>Ourense</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>18.832</t>
+          <t>14.883</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Málaga</t>
+          <t>Las Palmas</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>1.353.081</t>
+          <t>1.406.325</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Pontevedra</t>
+          <t>A Coruña</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>228.796</t>
+          <t>192.837</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Huesca</t>
+          <t>Lleida</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>74.011</t>
+          <t>73.619</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Teruel</t>
+          <t>Palencia</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>16.166</t>
+          <t>14.847</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Las Palmas</t>
+          <t>Girona</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>1.340.502</t>
+          <t>1.311.176</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -656,39 +656,39 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>169.359</t>
+          <t>163.885</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>León</t>
+          <t>Araba/Álava</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>67.991</t>
+          <t>69.361</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Ávila</t>
+          <t>Teruel</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>16.021</t>
+          <t>14.110</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Girona</t>
+          <t>Málaga</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>1.196.858</t>
+          <t>1.165.824</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -698,27 +698,27 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>157.449</t>
+          <t>143.522</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Lleida</t>
+          <t>Badajoz</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>65.206</t>
+          <t>67.905</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Ourense</t>
+          <t>Ávila</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>16.019</t>
+          <t>11.875</t>
         </is>
       </c>
     </row>
@@ -730,7 +730,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>869.473</t>
+          <t>931.281</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -740,17 +740,17 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>156.408</t>
+          <t>134.404</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Araba/Álava</t>
+          <t>Valladolid</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>62.971</t>
+          <t>65.840</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>14.609</t>
+          <t>11.740</t>
         </is>
       </c>
     </row>
@@ -772,7 +772,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>864.084</t>
+          <t>878.153</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -782,27 +782,27 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>140.424</t>
+          <t>134.019</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Badajoz</t>
+          <t>Lugo</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>62.274</t>
+          <t>62.093</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Cuenca</t>
+          <t>Melilla</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>9.942</t>
+          <t>9.917</t>
         </is>
       </c>
     </row>
@@ -814,17 +814,17 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>670.809</t>
+          <t>770.668</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Murcia</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>140.370</t>
+          <t>131.768</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -834,71 +834,71 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>61.460</t>
+          <t>58.552</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Guadalajara</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>9.645</t>
+          <t>9.353</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Sevilla</t>
+          <t>Valencia/València</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>565.563</t>
+          <t>539.821</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>Cantabria</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>133.759</t>
+          <t>129.837</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Valladolid</t>
+          <t>León</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>54.945</t>
+          <t>52.358</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Zamora</t>
+          <t>Guadalajara</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>9.420</t>
+          <t>7.957</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Valencia/València</t>
+          <t>Sevilla</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>521.022</t>
+          <t>477.546</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -908,7 +908,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>133.612</t>
+          <t>126.722</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -918,39 +918,39 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>54.821</t>
+          <t>40.563</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Melilla</t>
+          <t>Cuenca</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>8.693</t>
+          <t>7.812</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Granada</t>
+          <t>Bizkaia</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>348.310</t>
+          <t>319.611</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Cantabria</t>
+          <t>Navarra</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>131.352</t>
+          <t>123.818</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -960,17 +960,17 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>39.225</t>
+          <t>35.940</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Zamora</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>8.524</t>
+          <t>7.758</t>
         </is>
       </c>
     </row>
@@ -982,17 +982,17 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>300.346</t>
+          <t>296.870</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Navarra</t>
+          <t>Murcia</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>116.762</t>
+          <t>120.334</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1002,7 +1002,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>29.954</t>
+          <t>26.253</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -1012,7 +1012,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>6.342</t>
+          <t>5.661</t>
         </is>
       </c>
     </row>
